--- a/analysis/roi_list.xlsx
+++ b/analysis/roi_list.xlsx
@@ -1,31 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\thesis-matlab-pipeline\analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0D3227F-243B-4A60-A72A-26BB35950E8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91CF39BA-92DB-476F-BE67-CE538AC24A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1425" yWindow="2460" windowWidth="14490" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>ffa_right</t>
   </si>
@@ -45,9 +56,6 @@
     <t>session_n</t>
   </si>
   <si>
-    <t>JW</t>
-  </si>
-  <si>
     <t>SG</t>
   </si>
   <si>
@@ -66,22 +74,94 @@
     <t>JF</t>
   </si>
   <si>
-    <t>44, -54, -18</t>
-  </si>
-  <si>
-    <t>38, -76, -20</t>
-  </si>
-  <si>
-    <t>46, -56, -20</t>
-  </si>
-  <si>
-    <t>34, -84, -8</t>
-  </si>
-  <si>
-    <t>44, -58, -14</t>
-  </si>
-  <si>
-    <t>38, -62, -12</t>
+    <t>42 -52 -20</t>
+  </si>
+  <si>
+    <t>42 -54 -18</t>
+  </si>
+  <si>
+    <t>46 -56 -20</t>
+  </si>
+  <si>
+    <t>!: not detected in localizer</t>
+  </si>
+  <si>
+    <t>-42 -82 10</t>
+  </si>
+  <si>
+    <t>44 -78 -4</t>
+  </si>
+  <si>
+    <t>-42 -58 -18</t>
+  </si>
+  <si>
+    <t>-38 -74 -4</t>
+  </si>
+  <si>
+    <t>50 -74 - 10</t>
+  </si>
+  <si>
+    <t>-38 -50 -20</t>
+  </si>
+  <si>
+    <t>42 -78 -6</t>
+  </si>
+  <si>
+    <t>41 -72 -13</t>
+  </si>
+  <si>
+    <t>JW!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40 -48 -22 </t>
+  </si>
+  <si>
+    <t>-42 -80 -10</t>
+  </si>
+  <si>
+    <t>-40 -48 -22</t>
+  </si>
+  <si>
+    <t>-41 -72 -13</t>
+  </si>
+  <si>
+    <t>-44 -68 -14</t>
+  </si>
+  <si>
+    <t>34 -84 -8</t>
+  </si>
+  <si>
+    <t>44 -54 -14</t>
+  </si>
+  <si>
+    <t>-42 -52 -16</t>
+  </si>
+  <si>
+    <t>-40 -88 -4</t>
+  </si>
+  <si>
+    <t>40 -80 -12</t>
+  </si>
+  <si>
+    <t>44 -60 -14</t>
+  </si>
+  <si>
+    <t>-40 -52 -16</t>
+  </si>
+  <si>
+    <t>-46 -74 -14</t>
+  </si>
+  <si>
+    <t>-46 -58 -22</t>
+  </si>
+  <si>
+    <t>42 -44 -22</t>
+  </si>
+  <si>
+    <t>38 -62 -12</t>
+  </si>
+  <si>
+    <t>-44 -80 -2</t>
   </si>
 </sst>
 </file>
@@ -117,8 +197,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -399,15 +480,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -435,10 +515,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
+        <v>24</v>
+      </c>
+      <c r="C2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -446,10 +535,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
         <v>13</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -457,10 +555,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>12</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -468,10 +575,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>14</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -479,10 +595,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>31</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -490,10 +615,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>35</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -501,10 +635,24 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>39</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C10" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
